--- a/artfynd/A 25359-2026 artfynd.xlsx
+++ b/artfynd/A 25359-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129769188</v>
+        <v>129769187</v>
       </c>
       <c r="B2" t="n">
-        <v>57900</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511968</v>
+        <v>512033</v>
       </c>
       <c r="R2" t="n">
-        <v>6294552</v>
+        <v>6294534</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,6 +788,246 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129769862</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skruvaflyet, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>512015</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6294552</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Thulin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129769188</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skruvaflyet, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>511968</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6294552</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>

--- a/artfynd/A 25359-2026 artfynd.xlsx
+++ b/artfynd/A 25359-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769187</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769862</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,8 +1047,18 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769188</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>